--- a/processo_2/synthetic_proposals/PROPOSTA_023/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_023/ficha_pontuacao.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,17 +749,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" t="inlineStr"/>
     </row>
@@ -908,13 +908,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
@@ -950,7 +950,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -973,7 +973,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1067,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
@@ -1179,17 +1179,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1225,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1317,7 +1317,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1453,13 +1453,13 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="inlineStr"/>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1604,17 +1604,17 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
       </c>
       <c r="F56" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr"/>
     </row>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1652,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1790,11 +1790,15 @@
           <t>10</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
       <c r="E65" t="n">
         <v>2</v>
       </c>
-      <c r="F65" t="inlineStr"/>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
       <c r="G65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -1831,7 +1835,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1845,7 +1849,9 @@
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
+      <c r="F68" t="n">
+        <v>21</v>
+      </c>
       <c r="G68" t="inlineStr"/>
     </row>
   </sheetData>
